--- a/publish/Math/questions.xlsx
+++ b/publish/Math/questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anuj\opnsrc_try\ai\QuizWeb_Manual\publish\Math\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anuj\opnsrc_try\ai\QuizWeb_Manual\publish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE497295-DE11-46CD-9626-CAA1E89FE6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F988492E-D102-419F-98D8-43D4626BD81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,11 +20,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="679">
   <si>
     <t>Class: 9</t>
   </si>
   <si>
+    <t>Subject: Computer Science</t>
+  </si>
+  <si>
+    <t>Exam Type: Cycle Test III 2026-27 (Practice)</t>
+  </si>
+  <si>
     <t>Q.No</t>
   </si>
   <si>
@@ -40,30 +46,1920 @@
     <t>Correct</t>
   </si>
   <si>
+    <t>Option1</t>
+  </si>
+  <si>
+    <t>Option2</t>
+  </si>
+  <si>
+    <t>Option3</t>
+  </si>
+  <si>
+    <t>Option4</t>
+  </si>
+  <si>
+    <t>Option5</t>
+  </si>
+  <si>
+    <t>Option6</t>
+  </si>
+  <si>
+    <t>Option7</t>
+  </si>
+  <si>
+    <t>Option8</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>What does HTML stand for?</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>HyperText Markup Language</t>
+  </si>
+  <si>
+    <t>High Tech Modern Language</t>
+  </si>
+  <si>
+    <t>Hyperlink and Text Management Language</t>
+  </si>
+  <si>
+    <t>Home Tool Markup Language</t>
+  </si>
+  <si>
+    <t>Hyper Transfer Markup Language</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>HTML is a markup language used to create:</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
+    <t>Operating systems</t>
+  </si>
+  <si>
+    <t>Web pages and websites</t>
+  </si>
+  <si>
+    <t>Desktop applications only</t>
+  </si>
+  <si>
+    <t>Databases</t>
+  </si>
+  <si>
+    <t>Network cables</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Which tag is used to create a hyperlink in HTML?</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
+    <t>&lt;link&gt;</t>
+  </si>
+  <si>
+    <t>&lt;href&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;url&gt;</t>
+  </si>
+  <si>
+    <t>&lt;hyper&gt;</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Which attribute specifies the destination address of a link in HTML?</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
+    <t>src</t>
+  </si>
+  <si>
+    <t>alt</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>href</t>
+  </si>
+  <si>
+    <t>hl</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a paragraph?</t>
+  </si>
+  <si>
     <t>E</t>
   </si>
   <si>
+    <t>&lt;para&gt;</t>
+  </si>
+  <si>
+    <t>&lt;pt&gt;</t>
+  </si>
+  <si>
+    <t>&lt;text&gt;</t>
+  </si>
+  <si>
+    <t>&lt;pg&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Which tag is used for the largest heading in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;h1&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h6&gt;</t>
+  </si>
+  <si>
+    <t>&lt;hd&gt;</t>
+  </si>
+  <si>
+    <t>&lt;heading&gt;</t>
+  </si>
+  <si>
+    <t>&lt;hbig&gt;</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create an unordered list?</t>
+  </si>
+  <si>
+    <t>&lt;ol&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;</t>
+  </si>
+  <si>
+    <t>&lt;li&gt;</t>
+  </si>
+  <si>
+    <t>&lt;list&gt;</t>
+  </si>
+  <si>
+    <t>&lt;unlist&gt;</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create an ordered list?</t>
+  </si>
+  <si>
+    <t>&lt;ord&gt;</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a list item?</t>
+  </si>
+  <si>
+    <t>&lt;item&gt;</t>
+  </si>
+  <si>
+    <t>&lt;line&gt;</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a table?</t>
+  </si>
+  <si>
+    <t>&lt;td&gt;</t>
+  </si>
+  <si>
+    <t>&lt;tr&gt;</t>
+  </si>
+  <si>
+    <t>&lt;th&gt;</t>
+  </si>
+  <si>
+    <t>&lt;tab&gt;</t>
+  </si>
+  <si>
+    <t>&lt;table&gt;</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Which HTML tag creates a row in a table?</t>
+  </si>
+  <si>
+    <t>&lt;row&gt;</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Which HTML tag creates a header cell in a table?</t>
+  </si>
+  <si>
+    <t>&lt;header&gt;</t>
+  </si>
+  <si>
+    <t>&lt;table-head&gt;</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Which HTML tag creates a data cell in a table?</t>
+  </si>
+  <si>
+    <t>&lt;data&gt;</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to insert an image into a web page?</t>
+  </si>
+  <si>
+    <t>&lt;pic&gt;</t>
+  </si>
+  <si>
+    <t>&lt;picture&gt;</t>
+  </si>
+  <si>
+    <t>&lt;image&gt;</t>
+  </si>
+  <si>
+    <t>&lt;img&gt;</t>
+  </si>
+  <si>
+    <t>&lt;photo&gt;</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Which attribute specifies the file name of an image in the &lt;img&gt; tag?</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Which attribute provides alternative text for an image if it fails to load?</t>
+  </si>
+  <si>
+    <t>srcset</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a form for collecting user input?</t>
+  </si>
+  <si>
+    <t>&lt;input&gt;</t>
+  </si>
+  <si>
+    <t>&lt;form&gt;</t>
+  </si>
+  <si>
+    <t>&lt;field&gt;</t>
+  </si>
+  <si>
+    <t>&lt;area&gt;</t>
+  </si>
+  <si>
+    <t>&lt;label&gt;</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a text input field?</t>
+  </si>
+  <si>
+    <t>&lt;write&gt;</t>
+  </si>
+  <si>
+    <t>&lt;box&gt;</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a drop-down list?</t>
+  </si>
+  <si>
+    <t>&lt;dropdown&gt;</t>
+  </si>
+  <si>
+    <t>&lt;option&gt;</t>
+  </si>
+  <si>
+    <t>&lt;select&gt;</t>
+  </si>
+  <si>
+    <t>&lt;menu&gt;</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to create a division or container in a document?</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;container&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div&gt;</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Which tag is used to create a line break in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;lb&gt;</t>
+  </si>
+  <si>
+    <t>&lt;break&gt;</t>
+  </si>
+  <si>
+    <t>&lt;hr&gt;</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Which tag is used to draw a horizontal line in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;hline&gt;</t>
+  </si>
+  <si>
+    <t>&lt;separator&gt;</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Which tag makes text bold in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;strongly&gt;</t>
+  </si>
+  <si>
+    <t>&lt;bold&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;dark&gt;</t>
+  </si>
+  <si>
+    <t>&lt;fat&gt;</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Which tag makes text italic in HTML?</t>
+  </si>
+  <si>
+    <t>&lt;it&gt;</t>
+  </si>
+  <si>
+    <t>&lt;slanted&gt;</t>
+  </si>
+  <si>
+    <t>&lt;emph&gt;</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;</t>
+  </si>
+  <si>
+    <t>&lt;italics&gt;</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to write subscript text?</t>
+  </si>
+  <si>
+    <t>&lt;sup&gt;</t>
+  </si>
+  <si>
+    <t>&lt;down&gt;</t>
+  </si>
+  <si>
+    <t>&lt;below&gt;</t>
+  </si>
+  <si>
+    <t>&lt;small&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to write superscript text?</t>
+  </si>
+  <si>
+    <t>&lt;up&gt;</t>
+  </si>
+  <si>
+    <t>&lt;above&gt;</t>
+  </si>
+  <si>
+    <t>&lt;high&gt;</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Which tag contains the main visible content of a webpage?</t>
+  </si>
+  <si>
+    <t>&lt;head&gt;</t>
+  </si>
+  <si>
+    <t>&lt;body&gt;</t>
+  </si>
+  <si>
+    <t>&lt;title&gt;</t>
+  </si>
+  <si>
+    <t>&lt;main&gt;</t>
+  </si>
+  <si>
+    <t>&lt;html&gt;</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Which tag contains the title and metadata of an HTML document?</t>
+  </si>
+  <si>
+    <t>&lt;meta&gt;</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Which HTML tag is used to link an external stylesheet?</t>
+  </si>
+  <si>
+    <t>&lt;style&gt;</t>
+  </si>
+  <si>
+    <t>&lt;link rel&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sheet&gt;</t>
+  </si>
+  <si>
+    <t>&lt;css]</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Which attribute opens a hyperlink in a new browser tab?</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>What does CSS stand for?</t>
+  </si>
+  <si>
+    <t>Cascading Style Sheets</t>
+  </si>
+  <si>
+    <t>Computer Style System</t>
+  </si>
+  <si>
+    <t>Creative Style Sheets</t>
+  </si>
+  <si>
+    <t>Color and Style System</t>
+  </si>
+  <si>
+    <t>Cascading Size Sheets</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>What is CSS mainly used for?</t>
+  </si>
+  <si>
+    <t>Writing web page content</t>
+  </si>
+  <si>
+    <t>Styling the appearance of web pages</t>
+  </si>
+  <si>
+    <t>Creating computer programs</t>
+  </si>
+  <si>
+    <t>Storing data in databases</t>
+  </si>
+  <si>
+    <t>Sending emails</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Which type of CSS is written directly inside an HTML element?</t>
+  </si>
+  <si>
+    <t>External CSS</t>
+  </si>
+  <si>
+    <t>Internal CSS</t>
+  </si>
+  <si>
+    <t>Inline CSS</t>
+  </si>
+  <si>
+    <t>Embedded HTML</t>
+  </si>
+  <si>
+    <t>Global CSS</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Which type of CSS is written inside the &lt;style&gt; tag in the head section?</t>
+  </si>
+  <si>
+    <t>Local CSS</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Which type of CSS is written in a separate .css file?</t>
+  </si>
+  <si>
+    <t>Embedded CSS</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Which attribute is used to apply inline CSS to an element?</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
     <t>css</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to change the text colour?</t>
+  </si>
+  <si>
+    <t>text-color</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>font-color</t>
+  </si>
+  <si>
+    <t>background-color</t>
+  </si>
+  <si>
+    <t>text-style</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to set the background colour of an element?</t>
+  </si>
+  <si>
+    <t>bgcolor</t>
+  </si>
+  <si>
+    <t>fill</t>
+  </si>
+  <si>
+    <t>shade</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to change the size of text?</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>text-size</t>
+  </si>
+  <si>
+    <t>font-height</t>
+  </si>
+  <si>
+    <t>font-size</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to change the font typeface of text?</t>
+  </si>
+  <si>
+    <t>font-type</t>
+  </si>
+  <si>
+    <t>text-font</t>
+  </si>
+  <si>
+    <t>typeface</t>
+  </si>
+  <si>
+    <t>font</t>
+  </si>
+  <si>
+    <t>font-family</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Which CSS property is used to make text bold?</t>
+  </si>
+  <si>
+    <t>font-weight</t>
+  </si>
+  <si>
+    <t>font-bold</t>
+  </si>
+  <si>
+    <t>text-weight</t>
+  </si>
+  <si>
+    <t>bold</t>
+  </si>
+  <si>
+    <t>font-style</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Which CSS property creates rounded corners on an element?</t>
+  </si>
+  <si>
+    <t>corner-round</t>
+  </si>
+  <si>
+    <t>border-radius</t>
+  </si>
+  <si>
+    <t>round-border</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>curve</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Which CSS property sets the space between the content and the border of an element?</t>
+  </si>
+  <si>
+    <t>margin</t>
+  </si>
+  <si>
+    <t>spacing</t>
+  </si>
+  <si>
+    <t>padding</t>
+  </si>
+  <si>
+    <t>gap</t>
+  </si>
+  <si>
+    <t>space</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Which CSS property sets the space outside the border of an element?</t>
+  </si>
+  <si>
+    <t>outside</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Which selector is used to target an element by its id in CSS?</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>(empty)</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>:</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>What is the Internet?</t>
+  </si>
+  <si>
+    <t>A global network of interconnected computers</t>
+  </si>
+  <si>
+    <t>A single computer in a school</t>
+  </si>
+  <si>
+    <t>A type of web browser</t>
+  </si>
+  <si>
+    <t>A computer program</t>
+  </si>
+  <si>
+    <t>A mobile phone network</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>What does WWW stand for?</t>
+  </si>
+  <si>
+    <t>World Web Wide</t>
+  </si>
+  <si>
+    <t>World Wide Web</t>
+  </si>
+  <si>
+    <t>Web World Wide</t>
+  </si>
+  <si>
+    <t>World Wide Website</t>
+  </si>
+  <si>
+    <t>Wide Web World</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>A software program used to access and view websites is called a:</t>
+  </si>
+  <si>
+    <t>Search engine</t>
+  </si>
+  <si>
+    <t>Operating system</t>
+  </si>
+  <si>
+    <t>Web browser</t>
+  </si>
+  <si>
+    <t>Compiler</t>
+  </si>
+  <si>
+    <t>Modem</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Which of the following is a web browser?</t>
+  </si>
+  <si>
+    <t>Google Search</t>
+  </si>
+  <si>
+    <t>Google Drive</t>
+  </si>
+  <si>
+    <t>Google Docs</t>
+  </si>
+  <si>
+    <t>Google Chrome</t>
+  </si>
+  <si>
+    <t>Google Maps</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>A program or service used to find information on the Internet is called a:</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>Protocol</t>
+  </si>
+  <si>
+    <t>Server</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Which of the following is a search engine?</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>Notepad</t>
+  </si>
+  <si>
+    <t>Windows</t>
+  </si>
+  <si>
+    <t>VLC</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>What does URL stand for?</t>
+  </si>
+  <si>
+    <t>Universal Resource Link</t>
+  </si>
+  <si>
+    <t>Uniform Resource Locator</t>
+  </si>
+  <si>
+    <t>Uniform Resource Link</t>
+  </si>
+  <si>
+    <t>Universal Reference Locator</t>
+  </si>
+  <si>
+    <t>Unique Resource Location</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>A URL is the ______ of a resource available on the Internet.</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Which protocol is more secure for accessing websites?</t>
+  </si>
+  <si>
+    <t>HTTP</t>
+  </si>
+  <si>
+    <t>FTP</t>
+  </si>
+  <si>
+    <t>SMTP</t>
+  </si>
+  <si>
+    <t>HTTPS</t>
+  </si>
+  <si>
+    <t>Telnet</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>What does HTTP stand for?</t>
+  </si>
+  <si>
+    <t>HyperText Transport Program</t>
+  </si>
+  <si>
+    <t>High Text Transfer Protocol</t>
+  </si>
+  <si>
+    <t>Home Text Transfer Protocol</t>
+  </si>
+  <si>
+    <t>Hyperlink Transfer Protocol</t>
+  </si>
+  <si>
+    <t>HyperText Transfer Protocol</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>What does HTTPS stand for?</t>
+  </si>
+  <si>
+    <t>HyperText Transfer Protocol Secure</t>
+  </si>
+  <si>
+    <t>HyperText Transfer Protocol Server</t>
+  </si>
+  <si>
+    <t>High Transfer Protocol Secure</t>
+  </si>
+  <si>
+    <t>Hyperlink Transfer Protocol System</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>HTTPS keeps communication secure by encrypting data using:</t>
+  </si>
+  <si>
+    <t>SSL/TLS</t>
+  </si>
+  <si>
+    <t>HTML</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Which protocol is commonly used to transfer files between computers on a network?</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Which protocol is used to send email from a client to a mail server?</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>A collection of related web pages under one name is called a:</t>
+  </si>
+  <si>
+    <t>Web server</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>The first page that opens when you visit a website is called the:</t>
+  </si>
+  <si>
+    <t>Home page</t>
+  </si>
+  <si>
+    <t>Index page</t>
+  </si>
+  <si>
+    <t>Start page</t>
+  </si>
+  <si>
+    <t>Front page</t>
+  </si>
+  <si>
+    <t>Main page</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>The World Wide Web (WWW) was invented by:</t>
+  </si>
+  <si>
+    <t>Bill Gates</t>
+  </si>
+  <si>
+    <t>Tim Berners-Lee</t>
+  </si>
+  <si>
+    <t>Steve Jobs</t>
+  </si>
+  <si>
+    <t>Charles Babbage</t>
+  </si>
+  <si>
+    <t>Alan Turing</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>A word or phrase or image that you click to jump to another page is called a:</t>
+  </si>
+  <si>
+    <t>Web page</t>
+  </si>
+  <si>
+    <t>Browser</t>
+  </si>
+  <si>
+    <t>Hyperlink</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>The address of a website typed in the browser's address bar is its:</t>
+  </si>
+  <si>
+    <t>WWW</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>In the URL https://www.google.com, the domain name is:</t>
+  </si>
+  <si>
+    <t>https</t>
+  </si>
+  <si>
     <t>www</t>
   </si>
   <si>
+    <t>com</t>
+  </si>
+  <si>
+    <t>google</t>
+  </si>
+  <si>
+    <t>google.com</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>In a web address, "https" means the connection is:</t>
+  </si>
+  <si>
+    <t>Secure and encrypted</t>
+  </si>
+  <si>
+    <t>Unsafe</t>
+  </si>
+  <si>
+    <t>Slow</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Which of the following is a valid web address (URL) format?</t>
+  </si>
+  <si>
+    <t>www.example</t>
+  </si>
+  <si>
+    <t>https://www.example.com</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>com.example</t>
+  </si>
+  <si>
+    <t>//example</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Which device is commonly used to connect a computer to the Internet at home?</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>Scanner</t>
+  </si>
+  <si>
+    <t>Modem or router</t>
+  </si>
+  <si>
+    <t>Projector</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>Web pages on the Internet are written mainly in:</t>
+  </si>
+  <si>
+    <t>C++</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Pascal</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>A search engine finds web pages by:</t>
+  </si>
+  <si>
+    <t>Storing them on a CD</t>
+  </si>
+  <si>
+    <t>Asking users to type URLs</t>
+  </si>
+  <si>
+    <t>Using satellite signals</t>
+  </si>
+  <si>
+    <t>Browsing email</t>
+  </si>
+  <si>
+    <t>Searching and indexing the web using keywords</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Which software is commonly used for remote login and remote computer access?</t>
+  </si>
+  <si>
+    <t>AnyDesk</t>
+  </si>
+  <si>
+    <t>Calculator</t>
+  </si>
+  <si>
+    <t>Paint</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>AnyDesk is mainly used to:</t>
+  </si>
+  <si>
+    <t>Edit photos</t>
+  </si>
+  <si>
+    <t>Control a computer from a remote location</t>
+  </si>
+  <si>
+    <t>Play games</t>
+  </si>
+  <si>
+    <t>Record audio</t>
+  </si>
+  <si>
+    <t>Write documents</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Which of the following is a video conferencing tool?</t>
+  </si>
+  <si>
+    <t>Google Meet</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>Zoom and Microsoft Teams are commonly used for:</t>
+  </si>
+  <si>
+    <t>Designing graphics</t>
+  </si>
+  <si>
+    <t>Compiling programs</t>
+  </si>
+  <si>
+    <t>Storing files</t>
+  </si>
+  <si>
+    <t>Video conferencing and online meetings</t>
+  </si>
+  <si>
+    <t>Browsing the web</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>In an online meeting, the "Mute" button is used to:</t>
+  </si>
+  <si>
+    <t>Turn off your camera</t>
+  </si>
+  <si>
+    <t>End the meeting</t>
+  </si>
+  <si>
+    <t>Share the screen</t>
+  </si>
+  <si>
+    <t>Record the meeting</t>
+  </si>
+  <si>
+    <t>Turn off your microphone</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Remote desktop software allows a person to:</t>
+  </si>
+  <si>
+    <t>Access and control another computer over the Internet</t>
+  </si>
+  <si>
+    <t>Print documents on a network</t>
+  </si>
+  <si>
+    <t>Play CD-ROMs</t>
+  </si>
+  <si>
+    <t>Defragment the hard disk</t>
+  </si>
+  <si>
+    <t>Install drivers</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Which of the following is NOT a remote access tool?</t>
+  </si>
+  <si>
+    <t>TeamViewer</t>
+  </si>
+  <si>
+    <t>Chrome Remote Desktop</t>
+  </si>
+  <si>
+    <t>AnyDesk Remote</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>Which tool is often used for screen sharing during an online class?</t>
+  </si>
+  <si>
+    <t>Zoom</t>
+  </si>
+  <si>
+    <t>Word Processor</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>Remote access between two computers generally requires:</t>
+  </si>
+  <si>
+    <t>A printer</t>
+  </si>
+  <si>
+    <t>A scanner</t>
+  </si>
+  <si>
+    <t>A projector</t>
+  </si>
+  <si>
+    <t>An Internet connection between both computers</t>
+  </si>
+  <si>
+    <t>A television</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Which of the following is NOT a video conferencing application?</t>
+  </si>
+  <si>
+    <t>Microsoft Teams</t>
+  </si>
+  <si>
+    <t>Skype</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>UI stands for:</t>
+  </si>
+  <si>
+    <t>User Interface</t>
+  </si>
+  <si>
+    <t>User Internet</t>
+  </si>
+  <si>
+    <t>Universal Interface</t>
+  </si>
+  <si>
+    <t>User Input</t>
+  </si>
+  <si>
+    <t>Under Interface</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>UX stands for:</t>
+  </si>
+  <si>
+    <t>User External</t>
+  </si>
+  <si>
+    <t>User Experience</t>
+  </si>
+  <si>
+    <t>Universal Experience</t>
+  </si>
+  <si>
+    <t>User Expression</t>
+  </si>
+  <si>
+    <t>Unified Extension</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>The main purpose of UX design is to:</t>
+  </si>
+  <si>
+    <t>Write computer programs</t>
+  </si>
+  <si>
+    <t>Increase Internet speed</t>
+  </si>
+  <si>
+    <t>Improve the user's overall experience</t>
+  </si>
+  <si>
+    <t>Create databases</t>
+  </si>
+  <si>
+    <t>Design microchips</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>The main purpose of UI design is to:</t>
+  </si>
+  <si>
+    <t>Manage network cables</t>
+  </si>
+  <si>
+    <t>Write HTML documents</t>
+  </si>
+  <si>
+    <t>Compile code</t>
+  </si>
+  <si>
+    <t>Design the visual layout the user interacts with</t>
+  </si>
+  <si>
+    <t>Test hardware</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>A wireframe is best described as:</t>
+  </si>
+  <si>
+    <t>A finished, fully coded website</t>
+  </si>
+  <si>
+    <t>A type of web server</t>
+  </si>
+  <si>
+    <t>A programming language</t>
+  </si>
+  <si>
+    <t>A search engine</t>
+  </si>
+  <si>
+    <t>A basic visual layout or skeleton of a webpage or app</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>Social media is best described as a platform for:</t>
+  </si>
+  <si>
+    <t>Sharing content and interacting with others online</t>
+  </si>
+  <si>
+    <t>Storing hardware components</t>
+  </si>
+  <si>
+    <t>Installing software</t>
+  </si>
+  <si>
+    <t>Sending physical mail</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>Sharing your password publicly on social media is:</t>
+  </si>
+  <si>
+    <t>A safe practice</t>
+  </si>
+  <si>
+    <t>An unsafe practice</t>
+  </si>
+  <si>
+    <t>Required by law</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Recommended by teachers</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>Which of the following is a social media platform?</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>PowerPoint</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>A blog is best described as:</t>
+  </si>
+  <si>
+    <t>A type of hardware</t>
+  </si>
+  <si>
+    <t>An email address</t>
+  </si>
+  <si>
+    <t>A website with regularly updated articles or posts</t>
+  </si>
+  <si>
+    <t>A computer virus</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>Using the Internet to harass or threaten someone is called:</t>
+  </si>
+  <si>
+    <t>Browsing</t>
+  </si>
+  <si>
+    <t>Downloading</t>
+  </si>
+  <si>
+    <t>Uploading</t>
+  </si>
+  <si>
+    <t>Cyberbullying</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>Which of the following is a good password practice?</t>
+  </si>
+  <si>
+    <t>Using a strong, unique password</t>
+  </si>
+  <si>
+    <t>Using your date of birth</t>
+  </si>
+  <si>
+    <t>Sharing it with friends</t>
+  </si>
+  <si>
+    <t>Using 'password' as your password</t>
+  </si>
+  <si>
+    <t>Keeping the same password for every account</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>Clicking unknown links from suspicious websites is:</t>
+  </si>
+  <si>
+    <t>Usually safe</t>
+  </si>
+  <si>
+    <t>Unsafe and should be avoided</t>
+  </si>
+  <si>
+    <t>Required for studying</t>
+  </si>
+  <si>
+    <t>A good way to earn money</t>
+  </si>
+  <si>
+    <t>Recommended by experts</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Which action helps protect your privacy online?</t>
+  </si>
+  <si>
+    <t>Posting your address online</t>
+  </si>
+  <si>
+    <t>Sending passwords to friends</t>
+  </si>
+  <si>
+    <t>Not sharing personal details publicly</t>
+  </si>
+  <si>
+    <t>Accepting every friend request</t>
+  </si>
+  <si>
+    <t>Sharing your phone number</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>A "digital footprint" is best described as:</t>
+  </si>
+  <si>
+    <t>A type of computer virus</t>
+  </si>
+  <si>
+    <t>A software update</t>
+  </si>
+  <si>
+    <t>A storage device</t>
+  </si>
+  <si>
+    <t>The trail of data you leave behind online</t>
+  </si>
+  <si>
+    <t>A web browser</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>Which is a benefit of the Internet for students?</t>
+  </si>
+  <si>
+    <t>Wasting time on games only</t>
+  </si>
+  <si>
+    <t>Sending physical letters</t>
+  </si>
+  <si>
+    <t>Increasing pollution</t>
+  </si>
+  <si>
+    <t>Slowing down computers</t>
+  </si>
+  <si>
+    <t>Access to information and educational resources</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>WDLC stands for:</t>
+  </si>
+  <si>
+    <t>Web Development Life Cycle</t>
+  </si>
+  <si>
+    <t>Web Design and Layout Concept</t>
+  </si>
+  <si>
+    <t>Web Data Link Control</t>
+  </si>
+  <si>
+    <t>Web Document Language Code</t>
+  </si>
+  <si>
+    <t>Web Development Language Cycle</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>The first step in the WDLC is usually:</t>
+  </si>
+  <si>
+    <t>Debugging</t>
+  </si>
+  <si>
+    <t>Planning and analysis</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Publishing</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>In WDLC, the designing step mainly involves:</t>
+  </si>
+  <si>
+    <t>Writing the final code</t>
+  </si>
+  <si>
+    <t>Fixing bugs</t>
+  </si>
+  <si>
+    <t>Creating the layout, wireframe or prototype</t>
+  </si>
+  <si>
+    <t>Promoting the site</t>
+  </si>
+  <si>
+    <t>Buying hardware</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>In WDLC, the step where the website is actually coded is called:</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Implementation or development</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Testing a website is done to:</t>
+  </si>
+  <si>
+    <t>Delete the old website</t>
+  </si>
+  <si>
+    <t>Sell the website</t>
+  </si>
+  <si>
+    <t>Design the layout</t>
+  </si>
+  <si>
+    <t>Choose colours</t>
+  </si>
+  <si>
+    <t>Check that it works correctly without errors</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Publishing or deployment of a website means:</t>
+  </si>
+  <si>
+    <t>Making the website available on the Internet</t>
+  </si>
+  <si>
+    <t>Writing the HTML code</t>
+  </si>
+  <si>
+    <t>Designing wireframes</t>
+  </si>
+  <si>
+    <t>Testing the code</t>
+  </si>
+  <si>
+    <t>Collecting requirements</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>Which of the following is a step in the WDLC?</t>
+  </si>
+  <si>
+    <t>Printing</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>Singing</t>
+  </si>
+  <si>
+    <t>Saving money</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>A web developer mainly uses which languages to build a basic website?</t>
+  </si>
+  <si>
+    <t>Python and C++</t>
+  </si>
+  <si>
+    <t>C++ and Pascal</t>
+  </si>
+  <si>
+    <t>HTML, CSS and JavaScript</t>
+  </si>
+  <si>
+    <t>SQL and Excel</t>
+  </si>
+  <si>
+    <t>Photoshop and Paint</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Updating a website regularly to keep it working is part of:</t>
+  </si>
+  <si>
+    <t>Designing</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>A good website should be:</t>
+  </si>
+  <si>
+    <t>Very slow and confusing</t>
+  </si>
+  <si>
+    <t>Full of pop-up ads</t>
+  </si>
+  <si>
+    <t>With no text</t>
+  </si>
+  <si>
+    <t>Impossible to open</t>
+  </si>
+  <si>
+    <t>Easy to navigate and fast to load</t>
+  </si>
+  <si>
     <t>106</t>
   </si>
   <si>
@@ -161,45 +2057,6 @@
   </si>
   <si>
     <t>Numbers</t>
-  </si>
-  <si>
-    <t>option a</t>
-  </si>
-  <si>
-    <t>option c</t>
-  </si>
-  <si>
-    <t>option d</t>
-  </si>
-  <si>
-    <t>option e</t>
-  </si>
-  <si>
-    <t>option f</t>
-  </si>
-  <si>
-    <t>option g</t>
-  </si>
-  <si>
-    <t>option fe</t>
-  </si>
-  <si>
-    <t>option dd</t>
-  </si>
-  <si>
-    <t>Subject: Mathematics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exam Type: Cycle Test III </t>
-  </si>
-  <si>
-    <t>pendulum.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? What is this? </t>
-  </si>
-  <si>
-    <t>triangle.png</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +2897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
@@ -1050,210 +2907,3114 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="L4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="M4" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
         <v>43</v>
       </c>
-      <c r="H9" t="s">
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" t="s">
         <v>44</v>
       </c>
-      <c r="I9" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
         <v>45</v>
       </c>
-      <c r="J9" t="s">
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" t="s">
+        <v>116</v>
+      </c>
+      <c r="J21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" t="s">
+        <v>126</v>
+      </c>
+      <c r="J23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" t="s">
+        <v>132</v>
+      </c>
+      <c r="J24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" t="s">
+        <v>137</v>
+      </c>
+      <c r="H25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" t="s">
+        <v>146</v>
+      </c>
+      <c r="G27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H27" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" t="s">
+        <v>149</v>
+      </c>
+      <c r="J27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" t="s">
+        <v>155</v>
+      </c>
+      <c r="I28" t="s">
+        <v>156</v>
+      </c>
+      <c r="J28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" t="s">
+        <v>163</v>
+      </c>
+      <c r="J29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>160</v>
+      </c>
+      <c r="G30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H30" t="s">
+        <v>167</v>
+      </c>
+      <c r="I30" t="s">
+        <v>168</v>
+      </c>
+      <c r="J30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" t="s">
+        <v>172</v>
+      </c>
+      <c r="G31" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" t="s">
+        <v>174</v>
+      </c>
+      <c r="I31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" t="s">
+        <v>173</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>172</v>
+      </c>
+      <c r="I32" t="s">
+        <v>90</v>
+      </c>
+      <c r="J32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" t="s">
+        <v>183</v>
+      </c>
+      <c r="H33" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" t="s">
+        <v>36</v>
+      </c>
+      <c r="J33" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" t="s">
+        <v>190</v>
+      </c>
+      <c r="I34" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" t="s">
+        <v>192</v>
+      </c>
+      <c r="D35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>193</v>
+      </c>
+      <c r="G35" t="s">
+        <v>194</v>
+      </c>
+      <c r="H35" t="s">
+        <v>195</v>
+      </c>
+      <c r="I35" t="s">
+        <v>196</v>
+      </c>
+      <c r="J35" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" t="s">
+        <v>199</v>
+      </c>
+      <c r="D36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" t="s">
+        <v>200</v>
+      </c>
+      <c r="G36" t="s">
+        <v>201</v>
+      </c>
+      <c r="H36" t="s">
+        <v>202</v>
+      </c>
+      <c r="I36" t="s">
+        <v>203</v>
+      </c>
+      <c r="J36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" t="s">
+        <v>207</v>
+      </c>
+      <c r="G37" t="s">
+        <v>208</v>
+      </c>
+      <c r="H37" t="s">
+        <v>209</v>
+      </c>
+      <c r="I37" t="s">
+        <v>210</v>
+      </c>
+      <c r="J37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>212</v>
+      </c>
+      <c r="C38" t="s">
+        <v>213</v>
+      </c>
+      <c r="E38" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" t="s">
+        <v>209</v>
+      </c>
+      <c r="G38" t="s">
+        <v>207</v>
+      </c>
+      <c r="H38" t="s">
+        <v>211</v>
+      </c>
+      <c r="I38" t="s">
+        <v>208</v>
+      </c>
+      <c r="J38" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" t="s">
+        <v>216</v>
+      </c>
+      <c r="E39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" t="s">
+        <v>209</v>
+      </c>
+      <c r="G39" t="s">
+        <v>208</v>
+      </c>
+      <c r="H39" t="s">
+        <v>214</v>
+      </c>
+      <c r="I39" t="s">
+        <v>217</v>
+      </c>
+      <c r="J39" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" t="s">
+        <v>220</v>
+      </c>
+      <c r="H40" t="s">
+        <v>105</v>
+      </c>
+      <c r="I40" t="s">
+        <v>221</v>
+      </c>
+      <c r="J40" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+      <c r="C41" t="s">
+        <v>224</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>225</v>
+      </c>
+      <c r="G41" t="s">
+        <v>226</v>
+      </c>
+      <c r="H41" t="s">
+        <v>227</v>
+      </c>
+      <c r="I41" t="s">
+        <v>228</v>
+      </c>
+      <c r="J41" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>230</v>
+      </c>
+      <c r="C42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H42" t="s">
+        <v>228</v>
+      </c>
+      <c r="I42" t="s">
+        <v>233</v>
+      </c>
+      <c r="J42" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>235</v>
+      </c>
+      <c r="C43" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" t="s">
+        <v>237</v>
+      </c>
+      <c r="G43" t="s">
+        <v>238</v>
+      </c>
+      <c r="H43" t="s">
+        <v>239</v>
+      </c>
+      <c r="I43" t="s">
+        <v>240</v>
+      </c>
+      <c r="J43" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" t="s">
+        <v>243</v>
+      </c>
+      <c r="G44" t="s">
+        <v>244</v>
+      </c>
+      <c r="H44" t="s">
+        <v>245</v>
+      </c>
+      <c r="I44" t="s">
+        <v>246</v>
+      </c>
+      <c r="J44" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" t="s">
+        <v>249</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>250</v>
+      </c>
+      <c r="G45" t="s">
+        <v>251</v>
+      </c>
+      <c r="H45" t="s">
+        <v>252</v>
+      </c>
+      <c r="I45" t="s">
+        <v>253</v>
+      </c>
+      <c r="J45" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>255</v>
+      </c>
+      <c r="C46" t="s">
+        <v>256</v>
+      </c>
+      <c r="E46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" t="s">
+        <v>257</v>
+      </c>
+      <c r="G46" t="s">
+        <v>258</v>
+      </c>
+      <c r="H46" t="s">
+        <v>259</v>
+      </c>
+      <c r="I46" t="s">
+        <v>260</v>
+      </c>
+      <c r="J46" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C47" t="s">
+        <v>263</v>
+      </c>
+      <c r="E47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" t="s">
+        <v>264</v>
+      </c>
+      <c r="G47" t="s">
+        <v>265</v>
+      </c>
+      <c r="H47" t="s">
+        <v>266</v>
+      </c>
+      <c r="I47" t="s">
+        <v>267</v>
+      </c>
+      <c r="J47" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48" t="s">
+        <v>270</v>
+      </c>
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" t="s">
+        <v>265</v>
+      </c>
+      <c r="H48" t="s">
+        <v>267</v>
+      </c>
+      <c r="I48" t="s">
+        <v>264</v>
+      </c>
+      <c r="J48" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>272</v>
+      </c>
+      <c r="C49" t="s">
+        <v>273</v>
+      </c>
+      <c r="E49" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" t="s">
+        <v>274</v>
+      </c>
+      <c r="G49" t="s">
+        <v>275</v>
+      </c>
+      <c r="H49" t="s">
+        <v>276</v>
+      </c>
+      <c r="I49" t="s">
+        <v>277</v>
+      </c>
+      <c r="J49" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>279</v>
+      </c>
+      <c r="C50" t="s">
+        <v>280</v>
+      </c>
+      <c r="E50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
+        <v>281</v>
+      </c>
+      <c r="G50" t="s">
+        <v>282</v>
+      </c>
+      <c r="H50" t="s">
+        <v>283</v>
+      </c>
+      <c r="I50" t="s">
+        <v>284</v>
+      </c>
+      <c r="J50" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>286</v>
+      </c>
+      <c r="C51" t="s">
+        <v>287</v>
+      </c>
+      <c r="E51" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" t="s">
+        <v>288</v>
+      </c>
+      <c r="G51" t="s">
+        <v>289</v>
+      </c>
+      <c r="H51" t="s">
+        <v>290</v>
+      </c>
+      <c r="I51" t="s">
+        <v>291</v>
+      </c>
+      <c r="J51" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>293</v>
+      </c>
+      <c r="C52" t="s">
+        <v>294</v>
+      </c>
+      <c r="E52" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" t="s">
+        <v>295</v>
+      </c>
+      <c r="G52" t="s">
+        <v>296</v>
+      </c>
+      <c r="H52" t="s">
+        <v>297</v>
+      </c>
+      <c r="I52" t="s">
+        <v>298</v>
+      </c>
+      <c r="J52" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>300</v>
+      </c>
+      <c r="C53" t="s">
+        <v>301</v>
+      </c>
+      <c r="E53" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" t="s">
+        <v>302</v>
+      </c>
+      <c r="G53" t="s">
+        <v>303</v>
+      </c>
+      <c r="H53" t="s">
+        <v>304</v>
+      </c>
+      <c r="I53" t="s">
+        <v>305</v>
+      </c>
+      <c r="J53" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>307</v>
+      </c>
+      <c r="C54" t="s">
+        <v>308</v>
+      </c>
+      <c r="E54" t="s">
+        <v>51</v>
+      </c>
+      <c r="F54" t="s">
+        <v>297</v>
+      </c>
+      <c r="G54" t="s">
+        <v>309</v>
+      </c>
+      <c r="H54" t="s">
+        <v>310</v>
+      </c>
+      <c r="I54" t="s">
+        <v>311</v>
+      </c>
+      <c r="J54" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>312</v>
+      </c>
+      <c r="C55" t="s">
+        <v>313</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>314</v>
+      </c>
+      <c r="G55" t="s">
+        <v>315</v>
+      </c>
+      <c r="H55" t="s">
+        <v>316</v>
+      </c>
+      <c r="I55" t="s">
+        <v>317</v>
+      </c>
+      <c r="J55" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>319</v>
+      </c>
+      <c r="C56" t="s">
+        <v>320</v>
+      </c>
+      <c r="E56" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" t="s">
+        <v>321</v>
+      </c>
+      <c r="G56" t="s">
+        <v>322</v>
+      </c>
+      <c r="H56" t="s">
+        <v>323</v>
+      </c>
+      <c r="I56" t="s">
+        <v>324</v>
+      </c>
+      <c r="J56" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>326</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>327</v>
+      </c>
+      <c r="E57" t="s">
+        <v>35</v>
+      </c>
+      <c r="F57" t="s">
+        <v>328</v>
+      </c>
+      <c r="G57" t="s">
+        <v>329</v>
+      </c>
+      <c r="H57" t="s">
+        <v>330</v>
+      </c>
+      <c r="I57" t="s">
+        <v>331</v>
+      </c>
+      <c r="J57" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>333</v>
+      </c>
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>334</v>
+      </c>
+      <c r="E58" t="s">
+        <v>43</v>
+      </c>
+      <c r="F58" t="s">
+        <v>335</v>
+      </c>
+      <c r="G58" t="s">
+        <v>336</v>
+      </c>
+      <c r="H58" t="s">
+        <v>337</v>
+      </c>
+      <c r="I58" t="s">
+        <v>338</v>
+      </c>
+      <c r="J58" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>340</v>
+      </c>
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>341</v>
+      </c>
+      <c r="E59" t="s">
+        <v>51</v>
+      </c>
+      <c r="F59" t="s">
+        <v>342</v>
+      </c>
+      <c r="G59" t="s">
+        <v>343</v>
+      </c>
+      <c r="H59" t="s">
+        <v>344</v>
+      </c>
+      <c r="I59" t="s">
+        <v>345</v>
+      </c>
+      <c r="J59" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>347</v>
+      </c>
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>348</v>
+      </c>
+      <c r="E60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" t="s">
+        <v>349</v>
+      </c>
+      <c r="G60" t="s">
+        <v>350</v>
+      </c>
+      <c r="H60" t="s">
+        <v>351</v>
+      </c>
+      <c r="I60" t="s">
+        <v>352</v>
+      </c>
+      <c r="J60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>353</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>354</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" t="s">
+        <v>335</v>
+      </c>
+      <c r="G61" t="s">
+        <v>355</v>
+      </c>
+      <c r="H61" t="s">
+        <v>356</v>
+      </c>
+      <c r="I61" t="s">
+        <v>336</v>
+      </c>
+      <c r="J61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>358</v>
+      </c>
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>359</v>
+      </c>
+      <c r="E62" t="s">
+        <v>35</v>
+      </c>
+      <c r="F62" t="s">
+        <v>338</v>
+      </c>
+      <c r="G62" t="s">
+        <v>356</v>
+      </c>
+      <c r="H62" t="s">
+        <v>336</v>
+      </c>
+      <c r="I62" t="s">
+        <v>357</v>
+      </c>
+      <c r="J62" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>361</v>
+      </c>
+      <c r="E63" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" t="s">
+        <v>335</v>
+      </c>
+      <c r="G63" t="s">
+        <v>338</v>
+      </c>
+      <c r="H63" t="s">
+        <v>356</v>
+      </c>
+      <c r="I63" t="s">
+        <v>337</v>
+      </c>
+      <c r="J63" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>362</v>
+      </c>
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>363</v>
+      </c>
+      <c r="E64" t="s">
+        <v>51</v>
+      </c>
+      <c r="F64" t="s">
+        <v>297</v>
+      </c>
+      <c r="G64" t="s">
+        <v>364</v>
+      </c>
+      <c r="H64" t="s">
+        <v>295</v>
+      </c>
+      <c r="I64" t="s">
+        <v>357</v>
+      </c>
+      <c r="J64" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>365</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" t="s">
+        <v>366</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>367</v>
+      </c>
+      <c r="G65" t="s">
+        <v>368</v>
+      </c>
+      <c r="H65" t="s">
+        <v>369</v>
+      </c>
+      <c r="I65" t="s">
+        <v>370</v>
+      </c>
+      <c r="J65" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>372</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" t="s">
+        <v>373</v>
+      </c>
+      <c r="E66" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" t="s">
+        <v>374</v>
+      </c>
+      <c r="G66" t="s">
+        <v>375</v>
+      </c>
+      <c r="H66" t="s">
+        <v>376</v>
+      </c>
+      <c r="I66" t="s">
+        <v>377</v>
+      </c>
+      <c r="J66" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>379</v>
+      </c>
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" t="s">
+        <v>380</v>
+      </c>
+      <c r="E67" t="s">
+        <v>35</v>
+      </c>
+      <c r="F67" t="s">
+        <v>381</v>
+      </c>
+      <c r="G67" t="s">
+        <v>382</v>
+      </c>
+      <c r="H67" t="s">
+        <v>383</v>
+      </c>
+      <c r="I67" t="s">
+        <v>310</v>
+      </c>
+      <c r="J67" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>384</v>
+      </c>
+      <c r="B68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" t="s">
+        <v>385</v>
+      </c>
+      <c r="E68" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" t="s">
+        <v>356</v>
+      </c>
+      <c r="G68" t="s">
+        <v>335</v>
+      </c>
+      <c r="H68" t="s">
+        <v>386</v>
+      </c>
+      <c r="I68" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>387</v>
+      </c>
+      <c r="B69" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" t="s">
+        <v>388</v>
+      </c>
+      <c r="E69" t="s">
+        <v>51</v>
+      </c>
+      <c r="F69" t="s">
+        <v>389</v>
+      </c>
+      <c r="G69" t="s">
+        <v>390</v>
+      </c>
+      <c r="H69" t="s">
+        <v>391</v>
+      </c>
+      <c r="I69" t="s">
+        <v>392</v>
+      </c>
+      <c r="J69" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>394</v>
+      </c>
+      <c r="B70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" t="s">
+        <v>395</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>396</v>
+      </c>
+      <c r="G70" t="s">
+        <v>397</v>
+      </c>
+      <c r="H70" t="s">
+        <v>398</v>
+      </c>
+      <c r="I70" t="s">
+        <v>399</v>
+      </c>
+      <c r="J70" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>401</v>
+      </c>
+      <c r="B71" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" t="s">
+        <v>402</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" t="s">
+        <v>403</v>
+      </c>
+      <c r="G71" t="s">
+        <v>404</v>
+      </c>
+      <c r="H71" t="s">
+        <v>405</v>
+      </c>
+      <c r="I71" t="s">
+        <v>406</v>
+      </c>
+      <c r="J71" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>408</v>
+      </c>
+      <c r="B72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" t="s">
+        <v>409</v>
+      </c>
+      <c r="E72" t="s">
+        <v>35</v>
+      </c>
+      <c r="F72" t="s">
+        <v>410</v>
+      </c>
+      <c r="G72" t="s">
+        <v>411</v>
+      </c>
+      <c r="H72" t="s">
+        <v>412</v>
+      </c>
+      <c r="I72" t="s">
+        <v>413</v>
+      </c>
+      <c r="J72" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>415</v>
+      </c>
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" t="s">
+        <v>416</v>
+      </c>
+      <c r="E73" t="s">
+        <v>43</v>
+      </c>
+      <c r="F73" t="s">
+        <v>417</v>
+      </c>
+      <c r="G73" t="s">
+        <v>418</v>
+      </c>
+      <c r="H73" t="s">
+        <v>419</v>
+      </c>
+      <c r="I73" t="s">
+        <v>356</v>
+      </c>
+      <c r="J73" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>421</v>
+      </c>
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" t="s">
+        <v>422</v>
+      </c>
+      <c r="E74" t="s">
+        <v>51</v>
+      </c>
+      <c r="F74" t="s">
+        <v>423</v>
+      </c>
+      <c r="G74" t="s">
+        <v>424</v>
+      </c>
+      <c r="H74" t="s">
+        <v>425</v>
+      </c>
+      <c r="I74" t="s">
+        <v>426</v>
+      </c>
+      <c r="J74" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>428</v>
+      </c>
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" t="s">
+        <v>429</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>430</v>
+      </c>
+      <c r="G75" t="s">
+        <v>316</v>
+      </c>
+      <c r="H75" t="s">
+        <v>431</v>
+      </c>
+      <c r="I75" t="s">
+        <v>432</v>
+      </c>
+      <c r="J75" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>433</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" t="s">
+        <v>434</v>
+      </c>
+      <c r="E76" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76" t="s">
+        <v>435</v>
+      </c>
+      <c r="G76" t="s">
+        <v>436</v>
+      </c>
+      <c r="H76" t="s">
+        <v>437</v>
+      </c>
+      <c r="I76" t="s">
+        <v>438</v>
+      </c>
+      <c r="J76" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>440</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>441</v>
+      </c>
+      <c r="E77" t="s">
+        <v>35</v>
+      </c>
+      <c r="F77" t="s">
+        <v>302</v>
+      </c>
+      <c r="G77" t="s">
+        <v>305</v>
+      </c>
+      <c r="H77" t="s">
+        <v>442</v>
+      </c>
+      <c r="I77" t="s">
+        <v>303</v>
+      </c>
+      <c r="J77" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>443</v>
+      </c>
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
+        <v>444</v>
+      </c>
+      <c r="E78" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" t="s">
+        <v>445</v>
+      </c>
+      <c r="G78" t="s">
+        <v>446</v>
+      </c>
+      <c r="H78" t="s">
+        <v>447</v>
+      </c>
+      <c r="I78" t="s">
+        <v>448</v>
+      </c>
+      <c r="J78" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>450</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" t="s">
+        <v>451</v>
+      </c>
+      <c r="E79" t="s">
+        <v>51</v>
+      </c>
+      <c r="F79" t="s">
+        <v>452</v>
+      </c>
+      <c r="G79" t="s">
+        <v>453</v>
+      </c>
+      <c r="H79" t="s">
+        <v>454</v>
+      </c>
+      <c r="I79" t="s">
+        <v>455</v>
+      </c>
+      <c r="J79" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>457</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>458</v>
+      </c>
+      <c r="E80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" t="s">
+        <v>459</v>
+      </c>
+      <c r="G80" t="s">
+        <v>460</v>
+      </c>
+      <c r="H80" t="s">
+        <v>461</v>
+      </c>
+      <c r="I80" t="s">
+        <v>462</v>
+      </c>
+      <c r="J80" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>464</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>465</v>
+      </c>
+      <c r="E81" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" t="s">
+        <v>430</v>
+      </c>
+      <c r="G81" t="s">
+        <v>432</v>
+      </c>
+      <c r="H81" t="s">
+        <v>466</v>
+      </c>
+      <c r="I81" t="s">
+        <v>467</v>
+      </c>
+      <c r="J81" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>469</v>
+      </c>
+      <c r="B82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>470</v>
+      </c>
+      <c r="E82" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82" t="s">
+        <v>316</v>
+      </c>
+      <c r="G82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H82" t="s">
+        <v>471</v>
+      </c>
+      <c r="I82" t="s">
+        <v>432</v>
+      </c>
+      <c r="J82" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>473</v>
+      </c>
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" t="s">
+        <v>474</v>
+      </c>
+      <c r="E83" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" t="s">
+        <v>475</v>
+      </c>
+      <c r="G83" t="s">
+        <v>476</v>
+      </c>
+      <c r="H83" t="s">
+        <v>477</v>
+      </c>
+      <c r="I83" t="s">
+        <v>478</v>
+      </c>
+      <c r="J83" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>480</v>
+      </c>
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>481</v>
+      </c>
+      <c r="E84" t="s">
+        <v>51</v>
+      </c>
+      <c r="F84" t="s">
+        <v>442</v>
+      </c>
+      <c r="G84" t="s">
+        <v>471</v>
+      </c>
+      <c r="H84" t="s">
+        <v>482</v>
+      </c>
+      <c r="I84" t="s">
+        <v>483</v>
+      </c>
+      <c r="J84" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>484</v>
+      </c>
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>485</v>
+      </c>
+      <c r="E85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" t="s">
+        <v>486</v>
+      </c>
+      <c r="G85" t="s">
+        <v>487</v>
+      </c>
+      <c r="H85" t="s">
+        <v>488</v>
+      </c>
+      <c r="I85" t="s">
+        <v>489</v>
+      </c>
+      <c r="J85" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>491</v>
+      </c>
+      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" t="s">
+        <v>492</v>
+      </c>
+      <c r="E86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" t="s">
+        <v>493</v>
+      </c>
+      <c r="G86" t="s">
+        <v>494</v>
+      </c>
+      <c r="H86" t="s">
+        <v>495</v>
+      </c>
+      <c r="I86" t="s">
+        <v>496</v>
+      </c>
+      <c r="J86" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>498</v>
+      </c>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>499</v>
+      </c>
+      <c r="E87" t="s">
+        <v>35</v>
+      </c>
+      <c r="F87" t="s">
+        <v>500</v>
+      </c>
+      <c r="G87" t="s">
+        <v>501</v>
+      </c>
+      <c r="H87" t="s">
+        <v>502</v>
+      </c>
+      <c r="I87" t="s">
+        <v>503</v>
+      </c>
+      <c r="J87" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>505</v>
+      </c>
+      <c r="B88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" t="s">
+        <v>506</v>
+      </c>
+      <c r="E88" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" t="s">
+        <v>507</v>
+      </c>
+      <c r="G88" t="s">
+        <v>508</v>
+      </c>
+      <c r="H88" t="s">
+        <v>509</v>
+      </c>
+      <c r="I88" t="s">
+        <v>510</v>
+      </c>
+      <c r="J88" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>512</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>513</v>
+      </c>
+      <c r="E89" t="s">
+        <v>51</v>
+      </c>
+      <c r="F89" t="s">
+        <v>514</v>
+      </c>
+      <c r="G89" t="s">
+        <v>515</v>
+      </c>
+      <c r="H89" t="s">
+        <v>516</v>
+      </c>
+      <c r="I89" t="s">
+        <v>517</v>
+      </c>
+      <c r="J89" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>519</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" t="s">
+        <v>520</v>
+      </c>
+      <c r="E90" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" t="s">
+        <v>521</v>
+      </c>
+      <c r="G90" t="s">
+        <v>522</v>
+      </c>
+      <c r="H90" t="s">
+        <v>523</v>
+      </c>
+      <c r="I90" t="s">
+        <v>446</v>
+      </c>
+      <c r="J90" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>525</v>
+      </c>
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" t="s">
+        <v>526</v>
+      </c>
+      <c r="E91" t="s">
+        <v>27</v>
+      </c>
+      <c r="F91" t="s">
+        <v>527</v>
+      </c>
+      <c r="G91" t="s">
+        <v>528</v>
+      </c>
+      <c r="H91" t="s">
+        <v>529</v>
+      </c>
+      <c r="I91" t="s">
+        <v>530</v>
+      </c>
+      <c r="J91" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>532</v>
+      </c>
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>533</v>
+      </c>
+      <c r="E92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F92" t="s">
+        <v>315</v>
+      </c>
+      <c r="G92" t="s">
+        <v>316</v>
+      </c>
+      <c r="H92" t="s">
+        <v>534</v>
+      </c>
+      <c r="I92" t="s">
+        <v>317</v>
+      </c>
+      <c r="J92" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>536</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>537</v>
+      </c>
+      <c r="E93" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" t="s">
+        <v>538</v>
+      </c>
+      <c r="G93" t="s">
+        <v>517</v>
+      </c>
+      <c r="H93" t="s">
+        <v>539</v>
+      </c>
+      <c r="I93" t="s">
+        <v>540</v>
+      </c>
+      <c r="J93" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>542</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>543</v>
+      </c>
+      <c r="E94" t="s">
+        <v>43</v>
+      </c>
+      <c r="F94" t="s">
+        <v>544</v>
+      </c>
+      <c r="G94" t="s">
+        <v>545</v>
+      </c>
+      <c r="H94" t="s">
+        <v>546</v>
+      </c>
+      <c r="I94" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>548</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>549</v>
+      </c>
+      <c r="E95" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" t="s">
+        <v>550</v>
+      </c>
+      <c r="G95" t="s">
+        <v>551</v>
+      </c>
+      <c r="H95" t="s">
+        <v>552</v>
+      </c>
+      <c r="I95" t="s">
+        <v>553</v>
+      </c>
+      <c r="J95" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>555</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>556</v>
+      </c>
+      <c r="E96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s">
+        <v>557</v>
+      </c>
+      <c r="G96" t="s">
+        <v>558</v>
+      </c>
+      <c r="H96" t="s">
+        <v>559</v>
+      </c>
+      <c r="I96" t="s">
+        <v>560</v>
+      </c>
+      <c r="J96" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>562</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>563</v>
+      </c>
+      <c r="E97" t="s">
+        <v>35</v>
+      </c>
+      <c r="F97" t="s">
+        <v>564</v>
+      </c>
+      <c r="G97" t="s">
+        <v>565</v>
+      </c>
+      <c r="H97" t="s">
+        <v>566</v>
+      </c>
+      <c r="I97" t="s">
+        <v>567</v>
+      </c>
+      <c r="J97" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>569</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>570</v>
+      </c>
+      <c r="E98" t="s">
+        <v>43</v>
+      </c>
+      <c r="F98" t="s">
+        <v>571</v>
+      </c>
+      <c r="G98" t="s">
+        <v>572</v>
+      </c>
+      <c r="H98" t="s">
+        <v>573</v>
+      </c>
+      <c r="I98" t="s">
+        <v>574</v>
+      </c>
+      <c r="J98" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>576</v>
+      </c>
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
+        <v>577</v>
+      </c>
+      <c r="E99" t="s">
+        <v>51</v>
+      </c>
+      <c r="F99" t="s">
+        <v>578</v>
+      </c>
+      <c r="G99" t="s">
+        <v>579</v>
+      </c>
+      <c r="H99" t="s">
+        <v>580</v>
+      </c>
+      <c r="I99" t="s">
+        <v>581</v>
+      </c>
+      <c r="J99" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>583</v>
+      </c>
+      <c r="B100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" t="s">
+        <v>584</v>
+      </c>
+      <c r="E100" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" t="s">
+        <v>585</v>
+      </c>
+      <c r="G100" t="s">
+        <v>586</v>
+      </c>
+      <c r="H100" t="s">
+        <v>587</v>
+      </c>
+      <c r="I100" t="s">
+        <v>588</v>
+      </c>
+      <c r="J100" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>590</v>
+      </c>
+      <c r="B101" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" t="s">
+        <v>591</v>
+      </c>
+      <c r="E101" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" t="s">
+        <v>592</v>
+      </c>
+      <c r="G101" t="s">
+        <v>593</v>
+      </c>
+      <c r="H101" t="s">
+        <v>594</v>
+      </c>
+      <c r="I101" t="s">
+        <v>595</v>
+      </c>
+      <c r="J101" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>597</v>
+      </c>
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" t="s">
+        <v>598</v>
+      </c>
+      <c r="E102" t="s">
+        <v>35</v>
+      </c>
+      <c r="F102" t="s">
+        <v>599</v>
+      </c>
+      <c r="G102" t="s">
+        <v>600</v>
+      </c>
+      <c r="H102" t="s">
+        <v>601</v>
+      </c>
+      <c r="I102" t="s">
+        <v>602</v>
+      </c>
+      <c r="J102" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>604</v>
+      </c>
+      <c r="B103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" t="s">
+        <v>605</v>
+      </c>
+      <c r="E103" t="s">
+        <v>43</v>
+      </c>
+      <c r="F103" t="s">
+        <v>606</v>
+      </c>
+      <c r="G103" t="s">
+        <v>594</v>
+      </c>
+      <c r="H103" t="s">
+        <v>595</v>
+      </c>
+      <c r="I103" t="s">
+        <v>607</v>
+      </c>
+      <c r="J103" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>609</v>
+      </c>
+      <c r="B104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" t="s">
+        <v>610</v>
+      </c>
+      <c r="E104" t="s">
+        <v>51</v>
+      </c>
+      <c r="F104" t="s">
+        <v>611</v>
+      </c>
+      <c r="G104" t="s">
+        <v>612</v>
+      </c>
+      <c r="H104" t="s">
+        <v>613</v>
+      </c>
+      <c r="I104" t="s">
+        <v>614</v>
+      </c>
+      <c r="J104" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>616</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>617</v>
+      </c>
+      <c r="E105" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" t="s">
+        <v>618</v>
+      </c>
+      <c r="G105" t="s">
+        <v>619</v>
+      </c>
+      <c r="H105" t="s">
+        <v>620</v>
+      </c>
+      <c r="I105" t="s">
+        <v>621</v>
+      </c>
+      <c r="J105" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>623</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>624</v>
+      </c>
+      <c r="E106" t="s">
+        <v>27</v>
+      </c>
+      <c r="F106" t="s">
+        <v>625</v>
+      </c>
+      <c r="G106" t="s">
+        <v>595</v>
+      </c>
+      <c r="H106" t="s">
+        <v>626</v>
+      </c>
+      <c r="I106" t="s">
+        <v>627</v>
+      </c>
+      <c r="J106" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>629</v>
+      </c>
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>630</v>
+      </c>
+      <c r="E107" t="s">
+        <v>35</v>
+      </c>
+      <c r="F107" t="s">
+        <v>631</v>
+      </c>
+      <c r="G107" t="s">
+        <v>632</v>
+      </c>
+      <c r="H107" t="s">
+        <v>633</v>
+      </c>
+      <c r="I107" t="s">
+        <v>634</v>
+      </c>
+      <c r="J107" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>636</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>637</v>
+      </c>
+      <c r="E108" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" t="s">
+        <v>606</v>
+      </c>
+      <c r="G108" t="s">
+        <v>638</v>
+      </c>
+      <c r="H108" t="s">
+        <v>594</v>
+      </c>
+      <c r="I108" t="s">
+        <v>595</v>
+      </c>
+      <c r="J108" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>639</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>640</v>
+      </c>
+      <c r="E109" t="s">
+        <v>51</v>
+      </c>
+      <c r="F109" t="s">
+        <v>641</v>
+      </c>
+      <c r="G109" t="s">
+        <v>642</v>
+      </c>
+      <c r="H109" t="s">
+        <v>643</v>
+      </c>
+      <c r="I109" t="s">
+        <v>644</v>
+      </c>
+      <c r="J109" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>646</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
+        <v>647</v>
+      </c>
+      <c r="E110" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" t="s">
+        <v>648</v>
+      </c>
+      <c r="G110" t="s">
+        <v>649</v>
+      </c>
+      <c r="H110" t="s">
+        <v>650</v>
+      </c>
+      <c r="I110" t="s">
+        <v>651</v>
+      </c>
+      <c r="J110" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>653</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>654</v>
+      </c>
+      <c r="E111" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111" t="s">
+        <v>655</v>
+      </c>
+      <c r="G111" t="s">
+        <v>656</v>
+      </c>
+      <c r="H111" t="s">
+        <v>657</v>
+      </c>
+      <c r="I111" t="s">
+        <v>658</v>
+      </c>
+      <c r="J111" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>660</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>661</v>
+      </c>
+      <c r="E112" t="s">
+        <v>35</v>
+      </c>
+      <c r="F112" t="s">
+        <v>662</v>
+      </c>
+      <c r="G112" t="s">
+        <v>663</v>
+      </c>
+      <c r="H112" t="s">
+        <v>664</v>
+      </c>
+      <c r="I112" t="s">
+        <v>665</v>
+      </c>
+      <c r="J112" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>667</v>
+      </c>
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>668</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" t="s">
+        <v>43</v>
+      </c>
+      <c r="F113" t="s">
+        <v>390</v>
+      </c>
+      <c r="G113" t="s">
+        <v>669</v>
+      </c>
+      <c r="H113" t="s">
+        <v>670</v>
+      </c>
+      <c r="I113" t="s">
+        <v>671</v>
+      </c>
+      <c r="J113" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>672</v>
+      </c>
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" t="s">
+        <v>673</v>
+      </c>
+      <c r="D114" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" t="s">
+        <v>51</v>
+      </c>
+      <c r="F114" t="s">
+        <v>674</v>
+      </c>
+      <c r="G114" t="s">
+        <v>675</v>
+      </c>
+      <c r="H114" t="s">
+        <v>676</v>
+      </c>
+      <c r="I114" t="s">
+        <v>677</v>
+      </c>
+      <c r="J114" t="s">
+        <v>678</v>
       </c>
     </row>
   </sheetData>

--- a/publish/Math/questions.xlsx
+++ b/publish/Math/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anuj\opnsrc_try\ai\QuizWeb_Manual\publish\Math\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACD56C4-72D4-454C-9794-93B5EED0522B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACF7096-AF92-4BD4-BE6C-87E572F3B81F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Class: 9</t>
   </si>
@@ -73,217 +73,52 @@
     <t/>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
     <t>E</t>
   </si>
   <si>
-    <t>Google Search</t>
-  </si>
-  <si>
-    <t>Google Drive</t>
-  </si>
-  <si>
-    <t>Google Chrome</t>
-  </si>
-  <si>
-    <t>Google Maps</t>
-  </si>
-  <si>
-    <t>Notepad</t>
-  </si>
-  <si>
-    <t>AnyDesk</t>
-  </si>
-  <si>
-    <t>Calculator</t>
-  </si>
-  <si>
-    <t>Paint</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>Which of the following is a video conferencing tool?</t>
-  </si>
-  <si>
-    <t>Google Meet</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>Zoom and Microsoft Teams are commonly used for:</t>
-  </si>
-  <si>
-    <t>Designing graphics</t>
-  </si>
-  <si>
-    <t>Compiling programs</t>
-  </si>
-  <si>
-    <t>Storing files</t>
-  </si>
-  <si>
-    <t>Video conferencing and online meetings</t>
-  </si>
-  <si>
-    <t>Browsing the web</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>In an online meeting, the "Mute" button is used to:</t>
-  </si>
-  <si>
-    <t>Turn off your camera</t>
-  </si>
-  <si>
-    <t>End the meeting</t>
-  </si>
-  <si>
-    <t>Share the screen</t>
-  </si>
-  <si>
-    <t>Record the meeting</t>
-  </si>
-  <si>
-    <t>Turn off your microphone</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>Remote desktop software allows a person to:</t>
-  </si>
-  <si>
-    <t>Access and control another computer over the Internet</t>
-  </si>
-  <si>
-    <t>Print documents on a network</t>
-  </si>
-  <si>
-    <t>Play CD-ROMs</t>
-  </si>
-  <si>
-    <t>Defragment the hard disk</t>
-  </si>
-  <si>
-    <t>Install drivers</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>Which of the following is NOT a remote access tool?</t>
-  </si>
-  <si>
-    <t>TeamViewer</t>
-  </si>
-  <si>
-    <t>Chrome Remote Desktop</t>
-  </si>
-  <si>
-    <t>AnyDesk Remote</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>Which tool is often used for screen sharing during an online class?</t>
-  </si>
-  <si>
-    <t>Zoom</t>
-  </si>
-  <si>
-    <t>Word Processor</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>Remote access between two computers generally requires:</t>
-  </si>
-  <si>
-    <t>A printer</t>
-  </si>
-  <si>
-    <t>A scanner</t>
-  </si>
-  <si>
-    <t>A projector</t>
-  </si>
-  <si>
-    <t>An Internet connection between both computers</t>
-  </si>
-  <si>
-    <t>A television</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>Which of the following is NOT a video conferencing application?</t>
-  </si>
-  <si>
-    <t>Microsoft Teams</t>
-  </si>
-  <si>
-    <t>Skype</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>UI stands for:</t>
-  </si>
-  <si>
-    <t>User Interface</t>
-  </si>
-  <si>
-    <t>User Internet</t>
-  </si>
-  <si>
-    <t>Universal Interface</t>
-  </si>
-  <si>
-    <t>User Input</t>
-  </si>
-  <si>
-    <t>Under Interface</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>UX stands for:</t>
-  </si>
-  <si>
-    <t>User External</t>
-  </si>
-  <si>
-    <t>User Experience</t>
-  </si>
-  <si>
-    <t>Universal Experience</t>
-  </si>
-  <si>
-    <t>User Expression</t>
-  </si>
-  <si>
-    <t>Unified Extension</t>
+    <t>css</t>
+  </si>
+  <si>
+    <t>www</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Which of the following is a top-level domain?</t>
+  </si>
+  <si>
+    <t>http</t>
+  </si>
+  <si>
+    <t>html</t>
+  </si>
+  <si>
+    <t>.com</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>An ordered list in HTML displays items with:</t>
+  </si>
+  <si>
+    <t>Circles</t>
+  </si>
+  <si>
+    <t>Squares</t>
+  </si>
+  <si>
+    <t>Dashes</t>
+  </si>
+  <si>
+    <t>Check marks</t>
+  </si>
+  <si>
+    <t>Numbers</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
@@ -1185,292 +1020,66 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
       </c>
       <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
         <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
         <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" t="s">
-        <v>72</v>
-      </c>
-      <c r="I12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" t="s">
-        <v>77</v>
-      </c>
-      <c r="H13" t="s">
-        <v>78</v>
-      </c>
-      <c r="I13" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
